--- a/Risk Audit Spreadsheet/Risk Audit Spreadsheet.xlsx
+++ b/Risk Audit Spreadsheet/Risk Audit Spreadsheet.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emckclac-my.sharepoint.com/personal/k25008497_kcl_ac_uk/Documents/Documents/Hacking/GRC Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{F9853086-C409-462B-BF33-60EB2FBA107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40994F0A-67D0-426E-BD09-4CB97AFDA8E5}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{F9853086-C409-462B-BF33-60EB2FBA107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC91E324-1902-49A5-B28C-9DD74F0EF8FA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47DA8EE0-1C4E-4FE3-8919-915D9414350C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47DA8EE0-1C4E-4FE3-8919-915D9414350C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$15</definedName>
     <definedName name="Slicer_Risk_Level">#N/A</definedName>
     <definedName name="Slicer_System">#N/A</definedName>
   </definedNames>
@@ -154,9 +154,6 @@
     <t>Reused Employee Credentials</t>
   </si>
   <si>
-    <t>Insufficient Password Policy</t>
-  </si>
-  <si>
     <t>Internal AI Prompt Injection</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t>An attacker can obtain credentials and compromise mulitple systems across the company where credentials are reused</t>
   </si>
   <si>
-    <t>Impact (1-5)</t>
-  </si>
-  <si>
     <t>ISO 27001; NIST Cybersecurity Framework</t>
   </si>
   <si>
@@ -395,6 +389,12 @@
   </si>
   <si>
     <t>Reputation Damage; Legal Risk</t>
+  </si>
+  <si>
+    <t>Likelihood (1-5)</t>
+  </si>
+  <si>
+    <t>Insufficient Password Policy Enforcement</t>
   </si>
 </sst>
 </file>
@@ -426,7 +426,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,6 +451,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -464,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -485,6 +491,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -592,13 +601,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1639980</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>59018</xdr:rowOff>
+      <xdr:rowOff>7844</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>812426</xdr:colOff>
+      <xdr:colOff>809251</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>151089</xdr:rowOff>
+      <xdr:rowOff>106266</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -668,15 +677,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>640229</xdr:colOff>
+      <xdr:colOff>637054</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>62193</xdr:rowOff>
+      <xdr:rowOff>26894</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1636805</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>147917</xdr:rowOff>
+      <xdr:rowOff>106269</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -778,15 +787,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{01FC91C2-A17F-4A38-90EE-A5D1709F1A42}" name="Table1" displayName="Table1" ref="A1:L14" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L14" xr:uid="{1A6C096F-D4C8-49C9-8FB4-46C64CA9A6BF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{01FC91C2-A17F-4A38-90EE-A5D1709F1A42}" name="Table1" displayName="Table1" ref="A1:L15" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L15" xr:uid="{1A6C096F-D4C8-49C9-8FB4-46C64CA9A6BF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{20AEE4E5-96D9-477B-8D55-B7D0231B8520}" name="Risk ID" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{3F830A79-C1A7-4AE2-AC0B-1B64F78C2447}" name="Risk " dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{94EAEF3C-BBEC-40A7-BE52-DBAB4443B4A2}" name="System" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{33B4EDC6-C674-4AF0-835F-BAD2D9942CF9}" name="Risk Description" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{570DDAE2-D5BF-4C85-95E0-1AFA44FB7590}" name="Risk Scenario" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{E7776157-363D-4227-BB61-9FFA520C04DD}" name="Impact (1-5)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{E7776157-363D-4227-BB61-9FFA520C04DD}" name="Likelihood (1-5)" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{BA648207-ED71-4E6E-B395-64F92F9B8A74}" name="Risk Level " dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{8B6791B1-E5CD-41FD-AF0E-CAC5864A3955}" name="Relevant Framework" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{A6F6C96D-F239-40B9-9592-0A688F74E280}" name="Business Impact" dataDxfId="3"/>
@@ -1115,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6C096F-D4C8-49C9-8FB4-46C64CA9A6BF}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.08984375" style="2" customWidth="1"/>
@@ -1147,10 +1156,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
@@ -1168,7 +1177,7 @@
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1197,13 +1206,13 @@
         <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>17</v>
@@ -1235,13 +1244,13 @@
         <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>17</v>
@@ -1258,10 +1267,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F4" s="1">
         <v>5</v>
@@ -1270,16 +1279,16 @@
         <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>17</v>
@@ -1290,16 +1299,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1">
         <v>5</v>
@@ -1308,16 +1317,16 @@
         <v>13</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>17</v>
@@ -1328,16 +1337,16 @@
         <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -1346,16 +1355,16 @@
         <v>13</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>17</v>
@@ -1363,7 +1372,7 @@
     </row>
     <row r="7" spans="1:12" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
@@ -1372,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -1384,16 +1393,16 @@
         <v>13</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>17</v>
@@ -1401,37 +1410,37 @@
     </row>
     <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>17</v>
@@ -1439,7 +1448,7 @@
     </row>
     <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
@@ -1448,28 +1457,28 @@
         <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>17</v>
@@ -1477,193 +1486,207 @@
     </row>
     <row r="10" spans="1:12" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
